--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T08:14:05+00:00</t>
+    <t>2025-05-27T14:36:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1896,7 +1896,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-core-documentation-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-06T12:29:55+00:00</t>
+    <t>2025-10-13T08:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
